--- a/Methodology Library/DLT Earth Methodology Bounty Program/Emission Reductions from Safe Drinking Water Supply/calculations/VMR0015_calculations.xlsx
+++ b/Methodology Library/DLT Earth Methodology Bounty Program/Emission Reductions from Safe Drinking Water Supply/calculations/VMR0015_calculations.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="255">
   <si>
     <t xml:space="preserve">VMR0015 Calculation Workbook</t>
   </si>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">WorkedExample</t>
   </si>
   <si>
-    <t xml:space="preserve">Full numerical walk-through for a 100-household pilot site, 1 year</t>
+    <t xml:space="preserve">Canonical TC1 — must reproduce ER_total=10.00 tCO2e and mint=1000 base units (10.00 CER). Source-of-truth: evidence/CANONICAL_TC1.md.</t>
   </si>
   <si>
     <t xml:space="preserve">PolicyMapping</t>
@@ -554,132 +554,213 @@
     <t xml:space="preserve">status</t>
   </si>
   <si>
-    <t xml:space="preserve">Worked Example — 200-household solar-augmented pilot, 1 year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All inputs flow from EmissionFactors + Baseline + Project + Leakage sheets. Pilot scenario: 200-household solar-augmented treatment plant, 1 year.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Households</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline!D7 input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Persons served</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HH × p_hh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annual water demand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P × Q_pp × 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energy to boil water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q × E_boil / 1e6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leakage sheet</t>
+    <t xml:space="preserve">Worked Example — TC1 (canonical)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source-of-truth: evidence/CANONICAL_TC1.md. Do not edit without updating that file first.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mirrors customLogicBlock.calculate_report_fields. Output ER_total=10.00 tCO2e; mint=1000 base units (10.00 CER on token 0.0.8865898).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs (Monitoring Report VC, schema d0f009f5-44c6-438e-b852-02dbe831a079&amp;1.0.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BE_woody</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tCO2e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BE_fossil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE_electricity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE_transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE_manufacturing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE_aux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LE_woody</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LE_fossil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f_woody</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wq_pass_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fraction (&gt;=0.95 documentation gate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N_HH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monitoring_days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computation (verbatim from customLogicBlock.calculate_report_fields)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BE_woody + BE_fossil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE_electricity + PE_transport + PE_manufacturing + PE_aux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IF(f_woody&gt;0, LE_woody, 0) + LE_fossil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ER_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAX(0, BE_total - PE_total - LE_total)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mint_base_units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOOR(ER_total*100, 1)  (decimals=2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mint_readable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mint_base_units / 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Output write-paths (as the policy actually writes them)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">field5.field0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nested under field5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">field4.field0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nested under field4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">field6.field3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nested under field6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">field7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">top-level — read by mintDocumentBlock.rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mapping: Excel ↔ Policy customLogicBlock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How spreadsheet cells correspond to fields in calculate_project_fields / calculate_report_fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policy field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">customLogicBlock variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excel cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuel composition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">field2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fuel.field0 (woody fraction)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline!D10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project emissions group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">field4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pe.field1..field4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project!E8..E11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline emissions group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">field5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">be.field1 (woody) / field2 (fossil)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline!D18..D19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leakage group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">field6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leak.field1 (LE_woody) / field2 (LE_fossil)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leakage!E9..E10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ER total (output)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ER_total = BE_total − PE_total − LE_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WorkedExample!D26 (canonical TC1 = 10.00)</t>
   </si>
   <si>
     <t xml:space="preserve">Uncertainty discount</t>
   </si>
   <si>
-    <t xml:space="preserve">ER_net (CER tokens minted)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FINAL — minted as 0.0.8865898 tokens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mapping: Excel ↔ Policy customLogicBlock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How spreadsheet cells correspond to fields in calculate_project_fields / calculate_report_fields</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policy field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">customLogicBlock variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excel cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuel composition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">field2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fuel.field0 (woody fraction)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline!D10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project emissions group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">field4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pe.field1..field4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project!E8..E11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline emissions group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">field5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">be.field1 (woody) / field2 (fossil)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline!D18..D19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leakage group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">field6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">leak.field1 (LE_woody) / field2 (LE_fossil)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leakage!E9..E10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ER total (output)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">field7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ER_total = BE_total − PE_total − LE_total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ER_NetCalc!E9 → E11</t>
-  </si>
-  <si>
     <t xml:space="preserve">(NOT YET IN v1.0.0)</t>
   </si>
   <si>
@@ -699,9 +780,6 @@
   </si>
   <si>
     <t xml:space="preserve">ER_NetCalc!E12 surfaces FAIL flag instead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
   </si>
   <si>
     <t xml:space="preserve">• Policy v1.0.0 (currently published on Hedera) implements straight subtraction with silent negative-ER clamp.</t>
@@ -727,7 +805,7 @@
     <numFmt numFmtId="167" formatCode="0.00"/>
     <numFmt numFmtId="168" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -825,8 +903,44 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF555555"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF01696F"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -836,7 +950,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF01696F"/>
-        <bgColor rgb="FF008080"/>
+        <bgColor rgb="FF20808D"/>
       </patternFill>
     </fill>
     <fill>
@@ -848,7 +962,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE0F0F1"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <bgColor rgb="FFE8F4F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF20808D"/>
+        <bgColor rgb="FF339966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F4F1"/>
+        <bgColor rgb="FFE0F0F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -901,7 +1027,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -994,8 +1120,48 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1026,7 +1192,7 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF01696F"/>
+      <rgbColor rgb="FF20808D"/>
       <rgbColor rgb="FFD4D1CA"/>
       <rgbColor rgb="FF7A7974"/>
       <rgbColor rgb="FF9999FF"/>
@@ -1043,10 +1209,10 @@
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF01696F"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFE8F4F1"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -1059,7 +1225,7 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF555555"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
@@ -1408,7 +1574,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:F19"/>
+  <dimension ref="B1:F17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
@@ -1651,8 +1817,6 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2129,7 +2293,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:F13"/>
+  <dimension ref="B1:F11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
@@ -2282,8 +2446,6 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2481,193 +2643,428 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:E16"/>
+  <dimension ref="B1:F35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="23" t="s">
         <v>175</v>
       </c>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="25" t="s">
         <v>176</v>
       </c>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D7" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="C6" s="23" t="n">
-        <f aca="false">Baseline!D7</f>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="C11" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13" s="28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="C16" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="C17" s="28" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="C18" s="29" t="n">
         <v>200</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D18" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="C19" s="29" t="n">
+        <v>365</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="C7" s="23" t="n">
-        <f aca="false">Baseline!D14</f>
-        <v>900</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="8" t="s">
+      <c r="C22" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="24"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="D23" s="28" t="n">
+        <f aca="false">C8+C9</f>
+        <v>12</v>
+      </c>
+      <c r="E23" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="C8" s="23" t="n">
-        <f aca="false">Baseline!D15</f>
-        <v>1149750</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <f aca="false">Baseline!D16</f>
-        <v>0.390915</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
+      <c r="F23" s="24"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="D24" s="28" t="n">
+        <f aca="false">C10+C11+C12+C13</f>
+        <v>1</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="F24" s="24"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="D25" s="28" t="n">
+        <f aca="false">IF(C16&gt;0,C14,0)+C15</f>
+        <v>1</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="F25" s="24"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="D26" s="32" t="n">
+        <f aca="false">MAX(0,D23-D24-D25)</f>
+        <v>10</v>
+      </c>
+      <c r="E26" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="F26" s="24"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="D27" s="33" t="n">
+        <f aca="false">FLOOR(D26*100,1)</f>
+        <v>1000</v>
+      </c>
+      <c r="E27" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="F27" s="24"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="D28" s="28" t="n">
+        <f aca="false">D27/100</f>
+        <v>10</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="F28" s="24"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C10" s="16" t="n">
-        <f aca="false">Baseline!D21</f>
-        <v>16.59434175</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="s">
+      <c r="D32" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C11" s="16" t="n">
-        <f aca="false">Project!E16</f>
-        <v>4.1205070875</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="8" t="s">
+      <c r="D33" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C12" s="16" t="n">
-        <f aca="false">Leakage!E11</f>
-        <v>1.199718135</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <f aca="false">ER_NetCalc!E9</f>
-        <v>11.2741165275</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="C14" s="21" t="n">
-        <f aca="false">ER_NetCalc!E10</f>
-        <v>0.89</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="C15" s="17" t="n">
-        <f aca="false">ER_NetCalc!E11</f>
-        <v>10.033963709475</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="D34" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2697,162 +3094,162 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="7" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="8" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="8" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="8" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="8" t="s">
-        <v>188</v>
+        <v>243</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="8" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="13" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
+      <c r="B16" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
+      <c r="B17" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
+      <c r="B18" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
+      <c r="B19" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="4">
